--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -1,18 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Watchlist" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="No formal program" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="LinkedIn outreach" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Watchlist" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="No formal program" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LinkedIn outreach" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Underclassman programs" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Watchlist'!$A$2:$K$411</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Underclassman programs'!$A$2:$F$160</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -34960,4 +34962,4825 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F160"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Freshman/sophomore programs and postings (STEP/Explore/Ignite-style). Apply to these with the Class of 2029 graduation date. Sources: underclassmen-opportunities + summer-2027-internships GitHub repos, Extern's verified directory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Program / role</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Window / location / posted</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Source section</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Propel</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Both · 12 wks</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Aug-Oct 2026</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Verified directory (Extern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Future Engineer</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Freshman · 10-12 wks</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Nov 2026</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Verified directory (Extern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sophomore Analyst</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Bank of America</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Sophomore · 10 wks</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Sep-Nov 2026</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Verified directory (Extern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>First Year Insights</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Bloomberg</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Freshman · 1 day + virtual</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Spring 2027</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Verified directory (Extern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Rising Fellows</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Bridgewater</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Sophomore · 3-8 wks</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Dec 2026-Jan 2027</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Verified directory (Extern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>TEIP</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Both · 10 wks</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Dec 2026-Jan 2027</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Verified directory (Extern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Launch</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Citadel</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Sophomore · 11 wks</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Oct-Nov 2026</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Verified directory (Extern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Discover Citadel</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Citadel</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Both · 2 days</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Nov 2026</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Verified directory (Extern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Fellowships</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>D.E. Shaw</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Sophomore · 3 days</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Spring 2027</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Verified directory (Extern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>SWE Intern</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Dropbox</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Sophomore · 12 wks</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Dec 2026</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Verified directory (Extern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Thrive</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Sophomore · 10 wks</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Late Sep 2026</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Verified directory (Extern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Pathfinder</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Both · 12 wks</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Verified directory (Extern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>LINK</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Five Rings</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Sophomore · 5 days</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Spring 2027</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Verified directory (Extern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>ASDI</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Both · 12 wks</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Late Sep-Oct 2026 (2-4 wk window)</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Verified directory (Extern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>WiTTI</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>HRT</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Both (women + NB) · 2-4 wks (Jan)</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Verified directory (Extern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>FTTP</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Jane Street</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Freshman · Few days</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Jul-Aug 2026</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Verified directory (Extern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>JSIP</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Jane Street</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Both · Multi-week</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Verified directory (Extern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>JPMorgan</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Sophomore · 5 wks</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Nov 2026-Jan 2027</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Verified directory (Extern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>First Play</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Both · 12 wks</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Late Nov 2026 (2-wk window)</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Verified directory (Extern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Explore</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Both · 12 wks</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Sep-Oct 2026</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Verified directory (Extern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>MLH</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>All years · 12 wks</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Verified directory (Extern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Early Insights</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Morgan Stanley</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Sophomore · Short</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Feb-Mar 2027</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>Verified directory (Extern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Ignite</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Both · 12 wks</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Oct 2026 (2-wk window)</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Verified directory (Extern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>FutureFocus</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Optiver</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Both · 5 days</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Verified directory (Extern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Accelerate</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Palantir</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Soph + Junior · 10-12 wks</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Aug-Oct 2026</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Verified directory (Extern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>SWE Intern</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Both · 10 wks</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Verified directory (Extern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Futureforce Launchpad</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Sophomore · 10 wks</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Oct 2026-Feb 2027</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Verified directory (Extern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Tech Developer</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Both (URM) · 6 weeks</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Jan-Mar 2027</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Verified directory (Extern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Discovery Day</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>SIG</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Both · 2 days</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Verified directory (Extern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Freshman SWE</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Two Sigma</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Freshman · 10-12 wks</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Jul-Aug 2026</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>Verified directory (Extern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>UberSTAR</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Both · 10-12 wks</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Sep-Dec 2026</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Verified directory (Extern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Sophomore · 6-8 wks</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Sep-Oct 2026</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>Verified directory (Extern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>AI Builder Intern (Open to All Undergrads; No Class-Year Gate) — Deadline: Rolling</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Scale AI</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>San Francisco, CA Jun 17, 2026</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Internships</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern (Summer 2027, Python / C++ / Full Stack / C# .NET)</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Akuna Capital</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr"/>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Chicago, IL 2026-07-14</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern (apps reviewed from Aug 2026) 🇺🇸</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Anduril</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr"/>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA (multiple US) 2026-06-11</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern (Summer 2027)</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Aquatic Capital</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr"/>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Chicago, IL 2026-04-02</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Quantitative Developer Intern</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Arrowstreet Capital</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr"/>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Boston, MA 2026-07-09</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern (Spring 2027)</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>ASM</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr"/>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern I (Summer 2027) 🇺🇸</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>BAE Systems</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr"/>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Nashua, NH 2026-07-14</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Global Technology Summer Analyst, Cybersecurity Analyst 🛂</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Bank of America</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr"/>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>multiple US 2026-06-28</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Global Technology Summer Analyst, Business Analyst 🛂</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Bank of America</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr"/>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>multiple US 2026-06-28</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Software Developer Intern (Spring 2027) 🇺🇸</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Blue Origin</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr"/>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Seattle, WA (multiple US) 2026-06-10</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Avionics Software Intern (Spring 2027) 🇺🇸</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Blue Origin</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr"/>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Seattle, WA (multiple US) 2026-06-10</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern (Summer 2027) 🛂</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Circleback</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr"/>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>San Francisco, CA 2026-06-16</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Future Intern, Early Interest (Summer 2027, Software / AI/ML / Cyber) 🇺🇸</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>CloudFit Software</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr"/>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Lynchburg, VA -</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern / Research Intern, Interpretability (Summer 2027)</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>CTGT</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr"/>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>San Francisco, CA 2026-06-27</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Quantitative Developer Intern</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Cubist Systematic Strategies</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr"/>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>New York, NY -</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Software Developer Intern</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>D. E. Shaw</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr"/>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>New York, NY 2026-04-29</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Systems Engineering Intern</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>D. E. Shaw</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr"/>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>New York, NY -</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineering Intern ⏳</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>DimeHealth AI</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr"/>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>New York, NY -</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Information Technology Intern (2027 Summer) 🛂</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>DTCC</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr"/>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ (multiple US) 2026-07-08</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern (Summer 2027)</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Ellipsis Labs</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr"/>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>New York, NY 2026-03-27</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Software Developer Intern ⏳</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr"/>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Verona, WI -</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Software Developer Intern (Summer 2027)</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Five Rings</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr"/>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>New York, NY 2026-07-15</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Digital Technology Intern (Spring 2027)</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>GE Appliances</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr"/>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Louisville, KY 2026-06-01</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern, BS (Summer 2027)</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr"/>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Mountain View, CA (multiple US) 2026-07-20</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern (Summer 2027, C++ / Python)</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Hudson River Trading</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr"/>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>New York, NY (multiple) 2026-07-14</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern (Summer 2027)</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>IMC Trading</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr"/>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>Chicago, IL 2026-06-28</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Machine Learning Research Intern (Summer 2027)</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>IMC Trading</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr"/>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Chicago, IL 2026-06-28</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern (1) 🇺🇸</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Kudu Dynamics</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr"/>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>Chantilly, VA -</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern (2) 🇺🇸</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Kudu Dynamics</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr"/>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Chantilly, VA -</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern (3) 🇺🇸</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>Kudu Dynamics</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr"/>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Chantilly, VA -</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Technical Intern, Software / Cyber / AI (Spring 2027, remote)</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>LA-Tech.org</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr"/>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA / Remote (US) 2026-07-09</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern, Pixel Serving</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>LiveRamp</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr"/>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>New York, NY 2026-05-21</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Summer Intern (CS / Software / Engineering) 🇺🇸</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>LufCo</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr"/>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Aberdeen, MD -</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern 🇺🇸 ⏳</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>Naive</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr"/>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>San Francisco, CA / Remote (US) -</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Full Stack Engineering Intern 🇺🇸 ⏳</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Nash</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr"/>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>San Francisco, CA -</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern, Agent Platform / Full Stack (2026-2027)</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>Netic</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr"/>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>San Francisco, CA 2026-07-16</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern, BCI Applications ⏳</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Neuralink</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr"/>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Fremont, CA 2026-07-16</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern (Summer 2027, June Start)</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>Old Mission</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr"/>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>Chicago, IL 2026-07-15</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern (Austin)</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Optiver</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr"/>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Austin, TX 2026-06-28</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern (Chicago)</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>Optiver</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr"/>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>Chicago, IL 2026-06-28</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern (Summer 2027, grad 2028)</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Palantir</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr"/>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>New York, NY (multiple US) 2026-07-09</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern, Infrastructure (Summer 2027, grad 2028)</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>Palantir</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr"/>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>New York, NY (multiple US) 2026-07-09</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern, Production Infrastructure (Summer 2027, grad 2028)</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Palantir</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr"/>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>New York, NY (multiple US) 2026-07-09</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern, Defense Tech (Summer 2027, grad 2028)</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>Palantir</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr"/>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>Washington, DC (multiple US) 2026-07-09</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>Forward Deployed Software Engineer Intern, Commercial (Summer 2027, grad Dec 2027 / Spring 2028)</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Palantir</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr"/>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>New York, NY (multiple US) 2026-07-09</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>Year at Palantir, Forward Deployed Software Engineer Intern ⏳</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>Palantir</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr"/>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>New York, NY (multiple US) 2026-07-09</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern, Backend / Full Stack / ML (Winter 2027)</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>Rippling</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr"/>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>San Francisco, CA / New York, NY / Seattle, WA 2026-06-27</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern (Futureforce) 🔒</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr"/>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>San Francisco, CA -</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>Electrical Engineering Intern (Summer 2027)</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>Second Order Effects</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr"/>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>El Segundo, CA / Redmond, WA 2026-07-19</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern (Fall 2026 / Winter 2027)</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>Skydio</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr"/>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>San Mateo, CA 2026-05-06</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern 🇺🇸</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>Stoke Space</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr"/>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>Kent, WA 2026-05-05</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>Quantitative Strategy Developer Intern (Summer 2027, June start)</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>Susquehanna</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr"/>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>Bala Cynwyd, PA -</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>Trading System Engineering Intern 🇺🇸</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>Susquehanna</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr"/>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>Bala Cynwyd, PA -</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern (North America, Summer 2027)</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>The Trade Desk</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr"/>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Denver, CO (multiple US) 2026-07-16</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>Applied Scientist Intern, Monetization Technology (PhD, 2027 Start)</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr"/>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>San Jose, CA 2026-04-16</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>Quantitative Developer Intern (Summer 2027)</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>Tower Research Capital</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr"/>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>New York, NY / Chicago, IL 2026-07-06</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>Engineering Intern (12 roles: process, equipment, CIM / software)</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>TSMC Arizona</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr"/>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ 2026-06-04</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>AI Research Scientist Intern (MS / PhD)</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>Two Sigma</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr"/>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>New York, NY 2026-07-08</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern (Summer 2027, Uber Career Prep)</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr"/>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>San Francisco, CA / Seattle, WA / Sunnyvale, CA 2026-07-20</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>Engineering Intern (Summer 2027) 🛂 🇺🇸</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>Unison (GE Aerospace)</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr"/>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL 2026-07-16</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>Quantitative Developer Intern (2027)</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>Voloridge Investment Management</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr"/>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>Jupiter, FL 2026-06-15</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>Quant Developer Intern</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>Walleye Capital</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr"/>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>Boston, MA -</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern (Summer 2027)</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>Western Digital</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr"/>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>San Jose, CA 2026-07-20</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>Postings (community list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>🔥 CLOSING SOON]</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>AWS Student Builder Group Leader — Deadline: Aug 16, 2026 (11:59 PM PST)</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr"/>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>Ambassador Programs</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>AWS / NextGen</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>AWS Global University Program — Deadline: Rolling</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr"/>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>Ambassador Programs</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>Base44</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>Campus Impact Leaders (Founding Class) — Deadline: Rolling</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr"/>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>Ambassador Programs</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>Canva</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>Campus Canvassadors (Founding Cohort, Aug–Dec 2026) — Deadline: Rolling</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr"/>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>Ambassador Programs</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>🔥 CLOSING SOON]</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>CAVA</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>University of Minnesota Campus Brand Ambassador (Fall 2026) — Deadline: Aug 26, 2026</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr"/>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>Ambassador Programs</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>⏳ OPENS SOON]</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>Campus Expert — Deadline: Annual Window (Applications Open Each July; Next: July 2027)</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr"/>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>Ambassador Programs</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>Google Student Influencer Program (2026) — Deadline: Check site</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr"/>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="inlineStr">
+        <is>
+          <t>Ambassador Programs</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>Microsoft Learn Student Ambassadors — Deadline: Rolling</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr"/>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>Ambassador Programs</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>Monster Energy</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>College Ambassador Team (CAT) — Deadline: Check site</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr"/>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>Ambassador Programs</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI Student Collective (Campus Lead) — Deadline: Aug 31, 2026 (Japan, Korea, UK, Germany, France; US/Canada/India Cohort Closed)</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr"/>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>Ambassador Programs</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>Pearson Campus Ambassador — Deadline: Rolling</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr"/>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>Ambassador Programs</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>Princess Polly</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>College Ambassador — Deadline: Rolling</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr"/>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>Ambassador Programs</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>Red Bull</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>Student Marketeer — Deadline: Rolling</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr"/>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>Ambassador Programs</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>🔥 CLOSING SOON]</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>Uber Teen Ambassador (Seattle) — Deadline: Aug 15, 2026</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr"/>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>Ambassador Programs</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>🔥 CLOSING SOON]</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>Uber Teen Ambassador (Phoenix) — Deadline: Aug 15, 2026</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr"/>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="inlineStr">
+        <is>
+          <t>Ambassador Programs</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>Walmart / Satya Blends</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>Walmart UGC Creator — Deadline: Check site</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr"/>
+      <c r="E113" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>Ambassador Programs</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>Summer of Code</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>open-source, stipend, open to intl</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr"/>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>Pipelines (programs always open)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>Outreachy</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>Outreachy</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>open-source, stipend, open to intl</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr"/>
+      <c r="E115" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>Pipelines (programs always open)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>Software Undergrad Engineering Internship</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>SWE intern (undergrad)</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>rolling</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>Pipelines (programs open now)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>Machine Learning &amp; AI Undergrad Internship</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>ML / AI intern (undergrad)</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>rolling</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>Pipelines (programs open now)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Undergrad Engineering Internship</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>hardware intern (undergrad)</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>rolling</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="inlineStr">
+        <is>
+          <t>Pipelines (programs open now)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>Student Fellows Program</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>data and AI fellowship</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>check site</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>Pipelines (programs open now)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>2027 US Summer Internship, Early Interest</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>Dexcom</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>early interest pipeline</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>rolling</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>Pipelines (programs open now)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>Learn Student Ambassadors</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>ambassador program</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>rolling</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>Pipelines (programs open now)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>MLH Fellowship</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>MLH</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>remote SWE fellowship, stipend</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>rolling</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>Pipelines (programs open now)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>Neo Scholars</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>Neo</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>CS undergrad fellowship</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>approx June 14 to 30, 2026</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>Pipelines (programs open now)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>AI Builder, Emerging Talent</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>emerging talent program</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>check site</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>Pipelines (programs open now)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>2027 Summer Internships, Express Your Interest</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>Schonfeld</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>express interest pipeline, full roles open Aug 2026</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>rolling</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>Pipelines (programs open now)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>Ayn Rand Institute</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>Fountainhead Essay Contest (Grades 11–12) — Deadline: Sep 13, 2026 (Anthem contest closed May 31, 2026)</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr"/>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>Rising Freshmen &amp; Class of 2030 Opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>Coca-Cola Scholars Foundation</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>Coca-Cola Scholars Program (HS Senior; 3.0+ GPA)</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr"/>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>Rising Freshmen &amp; Class of 2030 Opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>Gates Foundation</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>The Gates Scholarship (Low-Income Minority HS Seniors)</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr"/>
+      <c r="E128" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t>Rising Freshmen &amp; Class of 2030 Opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>⏳ OPENS SOON]</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>Hagan Scholarship Foundation</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>Hagan Scholarship (HS Senior; 3.5+ GPA; Household Income ≤ $125K; 4-Yr Non-Profit College — No CC/Online)</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr"/>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="inlineStr">
+        <is>
+          <t>Rising Freshmen &amp; Class of 2030 Opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>Jane Street</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>WiSE - Women in Science &amp; Engineering (Class of 2030)</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr"/>
+      <c r="E130" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>Rising Freshmen &amp; Class of 2030 Opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>National Merit Scholarship Corporation</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>National Merit Scholarship (PSAT/NMSQT Junior Year)</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr"/>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>Rising Freshmen &amp; Class of 2030 Opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>Optimist International</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>Optimist International Essay Contest (Under 19 on Oct 1; 700–800 word essay; 2026-27 topic announced)</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr"/>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>Rising Freshmen &amp; Class of 2030 Opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>Posse Foundation</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>Posse Scholarship (Nomination-Based; Partner Cities)</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr"/>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="inlineStr">
+        <is>
+          <t>Rising Freshmen &amp; Class of 2030 Opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>QuestBridge</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>National College Match (HS Senior; Low-Income)</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr"/>
+      <c r="E134" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>Rising Freshmen &amp; Class of 2030 Opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>Regeneron / Society for Science</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>Regeneron Science Talent Search (HS Senior STEM Research)</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr"/>
+      <c r="E135" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>Rising Freshmen &amp; Class of 2030 Opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>Adobe NEXT// Campus Leader — Deadline: Check site</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr"/>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>Career Pathways Initiative</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>Career Pathways Initiative Fellowship — Deadline: Rolling</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr"/>
+      <c r="E137" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>🔥 CLOSING SOON]</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>Next-Gen Networking — Deadline: Aug 19, 2026 (11:59 PM PT) (Event: Sep 2, 2026)</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr"/>
+      <c r="E138" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F138" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>Databricks Student Fellows Program — Deadline: Check site</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr"/>
+      <c r="E139" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F139" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>ElevenLabs</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>ElevenLabs Ambassador Program — Deadline: Rolling</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr"/>
+      <c r="E140" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F140" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>GirlsWhoML</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>Thinking About Thinking 2026 Ambassador Programme — Deadline: Check site</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="inlineStr"/>
+      <c r="E141" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>Handshake</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>AI Fellowship Program — Deadline: Check site</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr"/>
+      <c r="E142" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F142" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>🔥 CLOSING SOON]</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>HeadStart Fellowship</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>HeadStart Fellowship (Fall 2026) — Deadline: Aug 28, 2026 (11:59 PM ET)</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr"/>
+      <c r="E143" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>IOScholarships</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>AWS re/Start — Deadline: Rolling (Cohort: Sep 15–Dec 15, 2026)</t>
+        </is>
+      </c>
+      <c r="D144" s="5" t="inlineStr"/>
+      <c r="E144" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>Jane Street</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>FTTP — First-Year Trading &amp; Technology Program — Deadline: Rolling (Sign Up to Be Notified)</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="inlineStr"/>
+      <c r="E145" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>Lime Connect</t>
+        </is>
+      </c>
+      <c r="C146" s="6" t="inlineStr">
+        <is>
+          <t>Lime Connect Network Membership — Deadline: Rolling</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="inlineStr"/>
+      <c r="E146" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F146" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>MLH (Major League Hacking)</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>MLH Fellowship — Deadline: Aug 31, 2026 (Fall Batch: Starts Sep 14, 2026)</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="inlineStr"/>
+      <c r="E147" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>MLT (Management Leadership for Tomorrow)</t>
+        </is>
+      </c>
+      <c r="C148" s="6" t="inlineStr">
+        <is>
+          <t>MLT Career Prep (Class of 2029) — Deadline: Aug 1, 2026 – Jan 15, 2027 (Phased)</t>
+        </is>
+      </c>
+      <c r="D148" s="5" t="inlineStr"/>
+      <c r="E148" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F148" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>National Geographic Society × The Nature Conservancy</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="inlineStr">
+        <is>
+          <t>Community Conservation: Data Visualization &amp; Mapping Externship — Deadline: Aug 30, 2026</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr"/>
+      <c r="E149" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F149" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
+        <is>
+          <t>NSN (National Sales Network)</t>
+        </is>
+      </c>
+      <c r="C150" s="6" t="inlineStr">
+        <is>
+          <t>2026 NSN Student Sales &amp; Marketing Conference — Deadline: Rolling (Event: Sep 12–14, 2026)</t>
+        </is>
+      </c>
+      <c r="D150" s="5" t="inlineStr"/>
+      <c r="E150" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F150" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B151" s="5" t="inlineStr">
+        <is>
+          <t>OpenTrade</t>
+        </is>
+      </c>
+      <c r="C151" s="6" t="inlineStr">
+        <is>
+          <t>OpenTrade Fellowship — Deadline: Rolling (Limited Spots)</t>
+        </is>
+      </c>
+      <c r="D151" s="5" t="inlineStr"/>
+      <c r="E151" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F151" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B152" s="5" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C152" s="6" t="inlineStr">
+        <is>
+          <t>PwC AI Externships — Deadline: Rolling</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="inlineStr"/>
+      <c r="E152" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F152" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>ServiceNow</t>
+        </is>
+      </c>
+      <c r="C153" s="6" t="inlineStr">
+        <is>
+          <t>Campus Leaders — Deadline: Rolling</t>
+        </is>
+      </c>
+      <c r="D153" s="5" t="inlineStr"/>
+      <c r="E153" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F153" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t>SHPE</t>
+        </is>
+      </c>
+      <c r="C154" s="6" t="inlineStr">
+        <is>
+          <t>2026 SHPE National Convention — Deadline: Check site (Event: Oct 28–31, 2026)</t>
+        </is>
+      </c>
+      <c r="D154" s="5" t="inlineStr"/>
+      <c r="E154" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F154" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>🔥 CLOSING SOON]</t>
+        </is>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C155" s="6" t="inlineStr">
+        <is>
+          <t>SoFi Sophomore Externship 2026 — Deadline: Check site (Event: Aug 18–19, 2026)</t>
+        </is>
+      </c>
+      <c r="D155" s="5" t="inlineStr"/>
+      <c r="E155" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F155" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>🔥 CLOSING SOON]</t>
+        </is>
+      </c>
+      <c r="B156" s="5" t="inlineStr">
+        <is>
+          <t>Stellic</t>
+        </is>
+      </c>
+      <c r="C156" s="6" t="inlineStr">
+        <is>
+          <t>The Pathfinders Challenge — Deadline: Aug 21, 2026 (Submissions Close)</t>
+        </is>
+      </c>
+      <c r="D156" s="5" t="inlineStr"/>
+      <c r="E156" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F156" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B157" s="5" t="inlineStr">
+        <is>
+          <t>The Home Depot</t>
+        </is>
+      </c>
+      <c r="C157" s="6" t="inlineStr">
+        <is>
+          <t>The Home Depot Externships (Multiple Tracks) — Deadline: Varies by Externship (Check Hub for Open Tracks)</t>
+        </is>
+      </c>
+      <c r="D157" s="5" t="inlineStr"/>
+      <c r="E157" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F157" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B158" s="5" t="inlineStr">
+        <is>
+          <t>WomenHack</t>
+        </is>
+      </c>
+      <c r="C158" s="6" t="inlineStr">
+        <is>
+          <t>Women in Tech Career Fair — Deadline: Varies per event</t>
+        </is>
+      </c>
+      <c r="D158" s="5" t="inlineStr"/>
+      <c r="E158" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F158" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>🔥 CLOSING SOON]</t>
+        </is>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>Y Combinator</t>
+        </is>
+      </c>
+      <c r="C159" s="6" t="inlineStr">
+        <is>
+          <t>YC 2027 Summer Internship Expo — Deadline: Check site (Event: Aug 15, 2026)</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr"/>
+      <c r="E159" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F159" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B160" s="5" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="C160" s="6" t="inlineStr">
+        <is>
+          <t>Student Researcher, BS/MS, Fall 2026 — Deadline: Nov 27, 2026 (Rolling; May Close Earlier)</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="inlineStr"/>
+      <c r="E160" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F160" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Research Programs</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:F160"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId158"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Watchlist" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="No formal program" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LinkedIn outreach" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Underclassman programs" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Watchlist" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="No formal program" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="LinkedIn outreach" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Underclassman programs" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Watchlist'!$A$2:$K$411</definedName>
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-08-15 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-08-16 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Watchlist'!$A$2:$K$411</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Underclassman programs'!$A$2:$F$160</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Underclassman programs'!$A$2:$F$155</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-08-16 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-08-17 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -34970,7 +34970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F160"/>
+  <dimension ref="A1:F155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -38179,17 +38179,17 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>🔥 CLOSING SOON]</t>
+          <t>Summer of Code</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>Uber Teen Ambassador (Seattle) — Deadline: Aug 15, 2026</t>
+          <t>open-source, stipend, open to intl</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr"/>
@@ -38200,24 +38200,24 @@
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>Ambassador Programs</t>
+          <t>Pipelines (programs always open)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>🔥 CLOSING SOON]</t>
+          <t>Outreachy</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Outreachy</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>Uber Teen Ambassador (Phoenix) — Deadline: Aug 15, 2026</t>
+          <t>open-source, stipend, open to intl</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr"/>
@@ -38228,27 +38228,31 @@
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>Ambassador Programs</t>
+          <t>Pipelines (programs always open)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>Software Undergrad Engineering Internship</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>Walmart / Satya Blends</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>Walmart UGC Creator — Deadline: Check site</t>
-        </is>
-      </c>
-      <c r="D113" s="5" t="inlineStr"/>
+          <t>SWE intern (undergrad)</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>rolling</t>
+        </is>
+      </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
           <t>apply</t>
@@ -38256,27 +38260,31 @@
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>Ambassador Programs</t>
+          <t>Pipelines (programs open now)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>Summer of Code</t>
+          <t>Machine Learning &amp; AI Undergrad Internship</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>open-source, stipend, open to intl</t>
-        </is>
-      </c>
-      <c r="D114" s="5" t="inlineStr"/>
+          <t>ML / AI intern (undergrad)</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>rolling</t>
+        </is>
+      </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
           <t>apply</t>
@@ -38284,27 +38292,31 @@
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>Pipelines (programs always open)</t>
+          <t>Pipelines (programs open now)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>Outreachy</t>
+          <t>Hardware Undergrad Engineering Internship</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>Outreachy</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>open-source, stipend, open to intl</t>
-        </is>
-      </c>
-      <c r="D115" s="5" t="inlineStr"/>
+          <t>hardware intern (undergrad)</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>rolling</t>
+        </is>
+      </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
           <t>apply</t>
@@ -38312,29 +38324,29 @@
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>Pipelines (programs always open)</t>
+          <t>Pipelines (programs open now)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>Software Undergrad Engineering Internship</t>
+          <t>Student Fellows Program</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>SWE intern (undergrad)</t>
+          <t>data and AI fellowship</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>rolling</t>
+          <t>check site</t>
         </is>
       </c>
       <c r="E116" s="7" t="inlineStr">
@@ -38351,17 +38363,17 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; AI Undergrad Internship</t>
+          <t>2027 US Summer Internship, Early Interest</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Dexcom</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>ML / AI intern (undergrad)</t>
+          <t>early interest pipeline</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
@@ -38383,17 +38395,17 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>Hardware Undergrad Engineering Internship</t>
+          <t>Learn Student Ambassadors</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>hardware intern (undergrad)</t>
+          <t>ambassador program</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
@@ -38415,22 +38427,22 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>Student Fellows Program</t>
+          <t>MLH Fellowship</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>MLH</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>data and AI fellowship</t>
+          <t>remote SWE fellowship, stipend</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>check site</t>
+          <t>rolling</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr">
@@ -38447,22 +38459,22 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>2027 US Summer Internship, Early Interest</t>
+          <t>Neo Scholars</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>Dexcom</t>
+          <t>Neo</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>early interest pipeline</t>
+          <t>CS undergrad fellowship</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>rolling</t>
+          <t>approx June 14 to 30, 2026</t>
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr">
@@ -38479,22 +38491,22 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>Learn Student Ambassadors</t>
+          <t>AI Builder, Emerging Talent</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>ambassador program</t>
+          <t>emerging talent program</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>rolling</t>
+          <t>check site</t>
         </is>
       </c>
       <c r="E121" s="7" t="inlineStr">
@@ -38511,17 +38523,17 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>MLH Fellowship</t>
+          <t>2027 Summer Internships, Express Your Interest</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>MLH</t>
+          <t>Schonfeld</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>remote SWE fellowship, stipend</t>
+          <t>express interest pipeline, full roles open Aug 2026</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
@@ -38543,24 +38555,20 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>Neo Scholars</t>
+          <t>⏳ OPENS SOON]</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>Neo</t>
+          <t>Ayn Rand Institute</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>CS undergrad fellowship</t>
-        </is>
-      </c>
-      <c r="D123" s="5" t="inlineStr">
-        <is>
-          <t>approx June 14 to 30, 2026</t>
-        </is>
-      </c>
+          <t>Fountainhead Essay Contest (Grades 11–12) — Deadline: Sep 13, 2026 (Anthem contest closed May 31, 2026)</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr"/>
       <c r="E123" s="7" t="inlineStr">
         <is>
           <t>apply</t>
@@ -38568,31 +38576,27 @@
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>Pipelines (programs open now)</t>
+          <t>Rising Freshmen &amp; Class of 2030 Opportunities</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>AI Builder, Emerging Talent</t>
+          <t>✅ OPEN]</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Coca-Cola Scholars Foundation</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>emerging talent program</t>
-        </is>
-      </c>
-      <c r="D124" s="5" t="inlineStr">
-        <is>
-          <t>check site</t>
-        </is>
-      </c>
+          <t>Coca-Cola Scholars Program (HS Senior; 3.0+ GPA)</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr"/>
       <c r="E124" s="7" t="inlineStr">
         <is>
           <t>apply</t>
@@ -38600,31 +38604,27 @@
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>Pipelines (programs open now)</t>
+          <t>Rising Freshmen &amp; Class of 2030 Opportunities</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>2027 Summer Internships, Express Your Interest</t>
+          <t>✅ OPEN]</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>Schonfeld</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>express interest pipeline, full roles open Aug 2026</t>
-        </is>
-      </c>
-      <c r="D125" s="5" t="inlineStr">
-        <is>
-          <t>rolling</t>
-        </is>
-      </c>
+          <t>The Gates Scholarship (Low-Income Minority HS Seniors)</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr"/>
       <c r="E125" s="7" t="inlineStr">
         <is>
           <t>apply</t>
@@ -38632,24 +38632,24 @@
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>Pipelines (programs open now)</t>
+          <t>Rising Freshmen &amp; Class of 2030 Opportunities</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>⏳ OPENS SOON]</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>Ayn Rand Institute</t>
+          <t>Hagan Scholarship Foundation</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>Fountainhead Essay Contest (Grades 11–12) — Deadline: Sep 13, 2026 (Anthem contest closed May 31, 2026)</t>
+          <t>Hagan Scholarship (HS Senior; 3.5+ GPA; Household Income ≤ $125K; 4-Yr Non-Profit College — No CC/Online)</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr"/>
@@ -38672,12 +38672,12 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>Coca-Cola Scholars Foundation</t>
+          <t>Jane Street</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>Coca-Cola Scholars Program (HS Senior; 3.0+ GPA)</t>
+          <t>WiSE - Women in Science &amp; Engineering (Class of 2030)</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr"/>
@@ -38700,12 +38700,12 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>National Merit Scholarship Corporation</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>The Gates Scholarship (Low-Income Minority HS Seniors)</t>
+          <t>National Merit Scholarship (PSAT/NMSQT Junior Year)</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr"/>
@@ -38723,17 +38723,17 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>⏳ OPENS SOON]</t>
+          <t>✅ OPEN]</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>Hagan Scholarship Foundation</t>
+          <t>Optimist International</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>Hagan Scholarship (HS Senior; 3.5+ GPA; Household Income ≤ $125K; 4-Yr Non-Profit College — No CC/Online)</t>
+          <t>Optimist International Essay Contest (Under 19 on Oct 1; 700–800 word essay; 2026-27 topic announced)</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr"/>
@@ -38756,12 +38756,12 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>Jane Street</t>
+          <t>Posse Foundation</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>WiSE - Women in Science &amp; Engineering (Class of 2030)</t>
+          <t>Posse Scholarship (Nomination-Based; Partner Cities)</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr"/>
@@ -38784,12 +38784,12 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>National Merit Scholarship Corporation</t>
+          <t>QuestBridge</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>National Merit Scholarship (PSAT/NMSQT Junior Year)</t>
+          <t>National College Match (HS Senior; Low-Income)</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr"/>
@@ -38812,12 +38812,12 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>Optimist International</t>
+          <t>Regeneron / Society for Science</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>Optimist International Essay Contest (Under 19 on Oct 1; 700–800 word essay; 2026-27 topic announced)</t>
+          <t>Regeneron Science Talent Search (HS Senior STEM Research)</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr"/>
@@ -38840,12 +38840,12 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>Posse Foundation</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>Posse Scholarship (Nomination-Based; Partner Cities)</t>
+          <t>Adobe NEXT// Campus Leader — Deadline: Check site</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr"/>
@@ -38856,7 +38856,7 @@
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>Rising Freshmen &amp; Class of 2030 Opportunities</t>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
         </is>
       </c>
     </row>
@@ -38868,12 +38868,12 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>QuestBridge</t>
+          <t>Career Pathways Initiative</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>National College Match (HS Senior; Low-Income)</t>
+          <t>Career Pathways Initiative Fellowship — Deadline: Rolling</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr"/>
@@ -38884,24 +38884,24 @@
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>Rising Freshmen &amp; Class of 2030 Opportunities</t>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>🔥 CLOSING SOON]</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>Regeneron / Society for Science</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>Regeneron Science Talent Search (HS Senior STEM Research)</t>
+          <t>Next-Gen Networking — Deadline: Aug 19, 2026 (11:59 PM PT) (Event: Sep 2, 2026)</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr"/>
@@ -38912,7 +38912,7 @@
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>Rising Freshmen &amp; Class of 2030 Opportunities</t>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
         </is>
       </c>
     </row>
@@ -38924,12 +38924,12 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>Adobe NEXT// Campus Leader — Deadline: Check site</t>
+          <t>Databricks Student Fellows Program — Deadline: Check site</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr"/>
@@ -38952,12 +38952,12 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>Career Pathways Initiative</t>
+          <t>ElevenLabs</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>Career Pathways Initiative Fellowship — Deadline: Rolling</t>
+          <t>ElevenLabs Ambassador Program — Deadline: Rolling</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr"/>
@@ -38975,17 +38975,17 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>🔥 CLOSING SOON]</t>
+          <t>✅ OPEN]</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>GirlsWhoML</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>Next-Gen Networking — Deadline: Aug 19, 2026 (11:59 PM PT) (Event: Sep 2, 2026)</t>
+          <t>Thinking About Thinking 2026 Ambassador Programme — Deadline: Check site</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr"/>
@@ -39008,12 +39008,12 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>Databricks Student Fellows Program — Deadline: Check site</t>
+          <t>AI Fellowship Program — Deadline: Check site</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr"/>
@@ -39031,17 +39031,17 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>🔥 CLOSING SOON]</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>ElevenLabs</t>
+          <t>HeadStart Fellowship</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>ElevenLabs Ambassador Program — Deadline: Rolling</t>
+          <t>HeadStart Fellowship (Fall 2026) — Deadline: Aug 28, 2026 (11:59 PM ET)</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr"/>
@@ -39064,12 +39064,12 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>GirlsWhoML</t>
+          <t>IOScholarships</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>Thinking About Thinking 2026 Ambassador Programme — Deadline: Check site</t>
+          <t>AWS re/Start — Deadline: Rolling (Cohort: Sep 15–Dec 15, 2026)</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr"/>
@@ -39092,12 +39092,12 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Jane Street</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>AI Fellowship Program — Deadline: Check site</t>
+          <t>FTTP — First-Year Trading &amp; Technology Program — Deadline: Rolling (Sign Up to Be Notified)</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr"/>
@@ -39115,17 +39115,17 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>🔥 CLOSING SOON]</t>
+          <t>✅ OPEN]</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>HeadStart Fellowship</t>
+          <t>Lime Connect</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>HeadStart Fellowship (Fall 2026) — Deadline: Aug 28, 2026 (11:59 PM ET)</t>
+          <t>Lime Connect Network Membership — Deadline: Rolling</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr"/>
@@ -39148,12 +39148,12 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>IOScholarships</t>
+          <t>MLH (Major League Hacking)</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>AWS re/Start — Deadline: Rolling (Cohort: Sep 15–Dec 15, 2026)</t>
+          <t>MLH Fellowship — Deadline: Aug 31, 2026 (Fall Batch: Starts Sep 14, 2026)</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr"/>
@@ -39176,12 +39176,12 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>Jane Street</t>
+          <t>MLT (Management Leadership for Tomorrow)</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>FTTP — First-Year Trading &amp; Technology Program — Deadline: Rolling (Sign Up to Be Notified)</t>
+          <t>MLT Career Prep (Class of 2029) — Deadline: Aug 1, 2026 – Jan 15, 2027 (Phased)</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr"/>
@@ -39199,17 +39199,17 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>🔥 CLOSING SOON]</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>Lime Connect</t>
+          <t>National Geographic Society × The Nature Conservancy</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>Lime Connect Network Membership — Deadline: Rolling</t>
+          <t>Community Conservation: Data Visualization &amp; Mapping Externship — Deadline: Aug 30, 2026</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr"/>
@@ -39232,12 +39232,12 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>MLH (Major League Hacking)</t>
+          <t>NSN (National Sales Network)</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>MLH Fellowship — Deadline: Aug 31, 2026 (Fall Batch: Starts Sep 14, 2026)</t>
+          <t>2026 NSN Student Sales &amp; Marketing Conference — Deadline: Rolling (Event: Sep 12–14, 2026)</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr"/>
@@ -39260,12 +39260,12 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>MLT (Management Leadership for Tomorrow)</t>
+          <t>OpenTrade</t>
         </is>
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>MLT Career Prep (Class of 2029) — Deadline: Aug 1, 2026 – Jan 15, 2027 (Phased)</t>
+          <t>OpenTrade Fellowship — Deadline: Rolling (Limited Spots)</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr"/>
@@ -39288,12 +39288,12 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>National Geographic Society × The Nature Conservancy</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>Community Conservation: Data Visualization &amp; Mapping Externship — Deadline: Aug 30, 2026</t>
+          <t>PwC AI Externships — Deadline: Rolling</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr"/>
@@ -39316,12 +39316,12 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>NSN (National Sales Network)</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>2026 NSN Student Sales &amp; Marketing Conference — Deadline: Rolling (Event: Sep 12–14, 2026)</t>
+          <t>Campus Leaders — Deadline: Rolling</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr"/>
@@ -39344,12 +39344,12 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>OpenTrade</t>
+          <t>SHPE</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>OpenTrade Fellowship — Deadline: Rolling (Limited Spots)</t>
+          <t>2026 SHPE National Convention — Deadline: Check site (Event: Oct 28–31, 2026)</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr"/>
@@ -39367,17 +39367,17 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>🔥 CLOSING SOON]</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>Stellic</t>
         </is>
       </c>
       <c r="C152" s="6" t="inlineStr">
         <is>
-          <t>PwC AI Externships — Deadline: Rolling</t>
+          <t>The Pathfinders Challenge — Deadline: Aug 21, 2026 (Submissions Close)</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr"/>
@@ -39400,12 +39400,12 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>Campus Leaders — Deadline: Rolling</t>
+          <t>The Home Depot Externships (Multiple Tracks) — Deadline: Varies by Externship (Check Hub for Open Tracks)</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr"/>
@@ -39428,12 +39428,12 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>SHPE</t>
+          <t>WomenHack</t>
         </is>
       </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
-          <t>2026 SHPE National Convention — Deadline: Check site (Event: Oct 28–31, 2026)</t>
+          <t>Women in Tech Career Fair — Deadline: Varies per event</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr"/>
@@ -39451,17 +39451,17 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>🔥 CLOSING SOON]</t>
+          <t>✅ OPEN]</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>SoFi Sophomore Externship 2026 — Deadline: Check site (Event: Aug 18–19, 2026)</t>
+          <t>Student Researcher, BS/MS, Fall 2026 — Deadline: Nov 27, 2026 (Rolling; May Close Earlier)</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr"/>
@@ -39472,152 +39472,12 @@
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="3" t="inlineStr">
-        <is>
-          <t>🔥 CLOSING SOON]</t>
-        </is>
-      </c>
-      <c r="B156" s="5" t="inlineStr">
-        <is>
-          <t>Stellic</t>
-        </is>
-      </c>
-      <c r="C156" s="6" t="inlineStr">
-        <is>
-          <t>The Pathfinders Challenge — Deadline: Aug 21, 2026 (Submissions Close)</t>
-        </is>
-      </c>
-      <c r="D156" s="5" t="inlineStr"/>
-      <c r="E156" s="7" t="inlineStr">
-        <is>
-          <t>apply</t>
-        </is>
-      </c>
-      <c r="F156" s="5" t="inlineStr">
-        <is>
-          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="3" t="inlineStr">
-        <is>
-          <t>✅ OPEN]</t>
-        </is>
-      </c>
-      <c r="B157" s="5" t="inlineStr">
-        <is>
-          <t>The Home Depot</t>
-        </is>
-      </c>
-      <c r="C157" s="6" t="inlineStr">
-        <is>
-          <t>The Home Depot Externships (Multiple Tracks) — Deadline: Varies by Externship (Check Hub for Open Tracks)</t>
-        </is>
-      </c>
-      <c r="D157" s="5" t="inlineStr"/>
-      <c r="E157" s="7" t="inlineStr">
-        <is>
-          <t>apply</t>
-        </is>
-      </c>
-      <c r="F157" s="5" t="inlineStr">
-        <is>
-          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="3" t="inlineStr">
-        <is>
-          <t>✅ OPEN]</t>
-        </is>
-      </c>
-      <c r="B158" s="5" t="inlineStr">
-        <is>
-          <t>WomenHack</t>
-        </is>
-      </c>
-      <c r="C158" s="6" t="inlineStr">
-        <is>
-          <t>Women in Tech Career Fair — Deadline: Varies per event</t>
-        </is>
-      </c>
-      <c r="D158" s="5" t="inlineStr"/>
-      <c r="E158" s="7" t="inlineStr">
-        <is>
-          <t>apply</t>
-        </is>
-      </c>
-      <c r="F158" s="5" t="inlineStr">
-        <is>
-          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="3" t="inlineStr">
-        <is>
-          <t>🔥 CLOSING SOON]</t>
-        </is>
-      </c>
-      <c r="B159" s="5" t="inlineStr">
-        <is>
-          <t>Y Combinator</t>
-        </is>
-      </c>
-      <c r="C159" s="6" t="inlineStr">
-        <is>
-          <t>YC 2027 Summer Internship Expo — Deadline: Check site (Event: Aug 15, 2026)</t>
-        </is>
-      </c>
-      <c r="D159" s="5" t="inlineStr"/>
-      <c r="E159" s="7" t="inlineStr">
-        <is>
-          <t>apply</t>
-        </is>
-      </c>
-      <c r="F159" s="5" t="inlineStr">
-        <is>
-          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="3" t="inlineStr">
-        <is>
-          <t>✅ OPEN]</t>
-        </is>
-      </c>
-      <c r="B160" s="5" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="C160" s="6" t="inlineStr">
-        <is>
-          <t>Student Researcher, BS/MS, Fall 2026 — Deadline: Nov 27, 2026 (Rolling; May Close Earlier)</t>
-        </is>
-      </c>
-      <c r="D160" s="5" t="inlineStr"/>
-      <c r="E160" s="7" t="inlineStr">
-        <is>
-          <t>apply</t>
-        </is>
-      </c>
-      <c r="F160" s="5" t="inlineStr">
-        <is>
           <t>Underclassmen Research Programs</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:F160"/>
+  <autoFilter ref="A2:F155"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -39775,11 +39635,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId151"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId158"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-08-17 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-08-18 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -38067,7 +38067,7 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>🔥 CLOSING SOON]</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
@@ -39143,7 +39143,7 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>🔥 CLOSING SOON]</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-08-18 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-08-19 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="K84" s="6" t="inlineStr">
         <is>
-          <t>Applications for summer 2027 expected to open around August 15 and close September 30, 2026 (rolling review; projected from prior cycle)</t>
+          <t>Applications for summer 2027 opened August 13 and close September 30, 2026 (rolling review from day one)</t>
         </is>
       </c>
     </row>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-08-19 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-08-20 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-08-20 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-08-21 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-08-23 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-08-24 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-08-24 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-08-25 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-08-25 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-08-26 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-08-26 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-08-27 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-08-27 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-08-28 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-08-28 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-08-29 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-08-29 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-08-30 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -39227,7 +39227,7 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>🔥 CLOSING SOON]</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-01 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-02 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -38547,7 +38547,7 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>🔥 CLOSING SOON]</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-02 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-03 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-03 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-04 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -3347,9 +3347,9 @@
           <t>Risk &amp; Financial Advisory Intern (incl. Cyber)  (1 of 6 tracks)</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>apply.deloitte.com/careers/SearchJobs</t>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>apply.deloitte.com job portal; program details on the offici</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -3357,11 +3357,7 @@
           <t>guide</t>
         </is>
       </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>Expect an online application, sometimes a recorded one-way video interview with roughly four to six behavioral prompts, then live rounds: typically two 30–45 minute interviews with Deloitte practitioners. Audit, tax, and Discovery interviews stay behavioral (use the STAR method); consulting candidat</t>
-        </is>
-      </c>
+      <c r="G52" s="6" t="inlineStr"/>
       <c r="H52" s="6" t="inlineStr"/>
       <c r="I52" s="6" t="inlineStr">
         <is>
@@ -23573,724 +23569,723 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F78" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F79" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F80" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F81" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F82" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F83" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F84" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F85" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F86" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F87" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F88" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F89" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F90" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F91" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F92" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F93" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F94" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F95" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F96" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F97" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F98" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F99" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F100" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F101" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F102" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F103" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F104" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F105" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F106" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F107" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F108" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F109" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F110" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F111" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F112" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F113" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F114" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F115" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F116" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F117" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F118" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F119" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F120" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F121" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F122" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F123" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F124" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F125" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F126" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F127" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F128" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F129" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F130" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F131" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F132" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F133" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F134" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F135" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F136" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F137" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F138" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F139" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F140" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F141" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F142" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F143" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F144" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F145" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F146" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F147" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F148" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F149" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F150" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F151" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F152" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F153" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F154" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F155" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F156" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F157" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F158" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F159" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F160" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F161" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F162" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F163" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F164" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F165" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F166" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F167" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F168" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F169" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F170" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F171" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F172" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E173" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F173" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F174" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E175" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F175" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E176" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F176" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F177" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E178" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F178" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F179" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E180" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F180" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E181" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F181" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F182" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F183" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F184" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F185" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F186" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F187" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F188" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F189" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F190" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F191" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F192" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F193" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E194" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F194" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F195" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F196" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F197" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F198" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F199" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F200" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E201" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F201" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F202" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F203" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F204" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F205" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F206" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F207" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E208" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F208" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F209" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E210" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F210" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E211" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F211" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E212" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F212" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E213" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F213" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E214" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F214" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E215" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F215" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E216" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F216" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E217" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F217" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E218" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F218" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E219" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F219" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E220" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F220" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E221" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F221" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E222" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F222" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E223" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F223" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F224" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E225" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F225" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E226" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F226" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E227" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F227" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E228" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F228" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E229" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F229" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E230" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F230" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E231" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F231" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E232" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F232" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E233" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F233" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E234" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F234" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E235" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F235" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E236" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F236" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E237" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F237" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E238" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F238" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E239" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F239" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E240" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F240" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E241" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F241" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E242" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F242" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E243" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F243" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E244" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F244" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E245" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F245" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E246" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F246" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E247" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F247" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E248" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F248" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E249" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F249" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E250" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F250" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E251" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F251" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E252" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F252" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E253" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F253" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E254" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F254" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E255" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F255" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E256" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F256" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E257" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F257" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E258" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F258" r:id="rId512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E259" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F259" r:id="rId514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E260" r:id="rId515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F260" r:id="rId516"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E261" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F261" r:id="rId518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E262" r:id="rId519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F262" r:id="rId520"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E263" r:id="rId521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F263" r:id="rId522"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E264" r:id="rId523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F264" r:id="rId524"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E265" r:id="rId525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F265" r:id="rId526"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E266" r:id="rId527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F266" r:id="rId528"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E267" r:id="rId529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F267" r:id="rId530"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E268" r:id="rId531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F268" r:id="rId532"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E269" r:id="rId533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F269" r:id="rId534"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E270" r:id="rId535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F270" r:id="rId536"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E271" r:id="rId537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F271" r:id="rId538"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E272" r:id="rId539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F272" r:id="rId540"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E273" r:id="rId541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F273" r:id="rId542"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E274" r:id="rId543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F274" r:id="rId544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E275" r:id="rId545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F275" r:id="rId546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E276" r:id="rId547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F276" r:id="rId548"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E277" r:id="rId549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F277" r:id="rId550"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E278" r:id="rId551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F278" r:id="rId552"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E279" r:id="rId553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F279" r:id="rId554"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E280" r:id="rId555"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F280" r:id="rId556"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E281" r:id="rId557"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F281" r:id="rId558"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E282" r:id="rId559"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F282" r:id="rId560"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E283" r:id="rId561"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F283" r:id="rId562"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E284" r:id="rId563"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F284" r:id="rId564"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E285" r:id="rId565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F285" r:id="rId566"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E286" r:id="rId567"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F286" r:id="rId568"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E287" r:id="rId569"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F287" r:id="rId570"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E288" r:id="rId571"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F288" r:id="rId572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E289" r:id="rId573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F289" r:id="rId574"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E290" r:id="rId575"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F290" r:id="rId576"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E291" r:id="rId577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F291" r:id="rId578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E292" r:id="rId579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F292" r:id="rId580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E293" r:id="rId581"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F293" r:id="rId582"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E294" r:id="rId583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F294" r:id="rId584"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E295" r:id="rId585"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F295" r:id="rId586"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E296" r:id="rId587"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F296" r:id="rId588"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E297" r:id="rId589"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F297" r:id="rId590"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E298" r:id="rId591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F298" r:id="rId592"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E299" r:id="rId593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F299" r:id="rId594"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E300" r:id="rId595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F300" r:id="rId596"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E301" r:id="rId597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F301" r:id="rId598"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E302" r:id="rId599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F302" r:id="rId600"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E303" r:id="rId601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F303" r:id="rId602"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E304" r:id="rId603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F304" r:id="rId604"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E305" r:id="rId605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F305" r:id="rId606"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E306" r:id="rId607"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F306" r:id="rId608"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E307" r:id="rId609"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F307" r:id="rId610"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E308" r:id="rId611"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F308" r:id="rId612"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E309" r:id="rId613"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F309" r:id="rId614"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E310" r:id="rId615"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F310" r:id="rId616"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E311" r:id="rId617"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F311" r:id="rId618"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E312" r:id="rId619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F312" r:id="rId620"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E313" r:id="rId621"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F313" r:id="rId622"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E314" r:id="rId623"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F314" r:id="rId624"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E315" r:id="rId625"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F315" r:id="rId626"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E316" r:id="rId627"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F316" r:id="rId628"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E317" r:id="rId629"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F317" r:id="rId630"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E318" r:id="rId631"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F318" r:id="rId632"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E319" r:id="rId633"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F319" r:id="rId634"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E320" r:id="rId635"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F320" r:id="rId636"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E321" r:id="rId637"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F321" r:id="rId638"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E322" r:id="rId639"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F322" r:id="rId640"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E323" r:id="rId641"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F323" r:id="rId642"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E324" r:id="rId643"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F324" r:id="rId644"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E325" r:id="rId645"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F325" r:id="rId646"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E326" r:id="rId647"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F326" r:id="rId648"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E327" r:id="rId649"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F327" r:id="rId650"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E328" r:id="rId651"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F328" r:id="rId652"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E329" r:id="rId653"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F329" r:id="rId654"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E330" r:id="rId655"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F330" r:id="rId656"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E331" r:id="rId657"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F331" r:id="rId658"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E332" r:id="rId659"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F332" r:id="rId660"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E333" r:id="rId661"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F333" r:id="rId662"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E334" r:id="rId663"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F334" r:id="rId664"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E335" r:id="rId665"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F335" r:id="rId666"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E336" r:id="rId667"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F336" r:id="rId668"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E337" r:id="rId669"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F337" r:id="rId670"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E338" r:id="rId671"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F338" r:id="rId672"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E339" r:id="rId673"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F339" r:id="rId674"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E340" r:id="rId675"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F340" r:id="rId676"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E341" r:id="rId677"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F341" r:id="rId678"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E342" r:id="rId679"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F342" r:id="rId680"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E343" r:id="rId681"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F343" r:id="rId682"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E344" r:id="rId683"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F344" r:id="rId684"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E345" r:id="rId685"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F345" r:id="rId686"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E346" r:id="rId687"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F346" r:id="rId688"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E347" r:id="rId689"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F347" r:id="rId690"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E348" r:id="rId691"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F348" r:id="rId692"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E349" r:id="rId693"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F349" r:id="rId694"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E350" r:id="rId695"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F350" r:id="rId696"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E351" r:id="rId697"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F351" r:id="rId698"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E352" r:id="rId699"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F352" r:id="rId700"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E353" r:id="rId701"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F353" r:id="rId702"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E354" r:id="rId703"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F354" r:id="rId704"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E355" r:id="rId705"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F355" r:id="rId706"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E356" r:id="rId707"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F356" r:id="rId708"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E357" r:id="rId709"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F357" r:id="rId710"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E358" r:id="rId711"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F358" r:id="rId712"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E359" r:id="rId713"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F359" r:id="rId714"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E360" r:id="rId715"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F360" r:id="rId716"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E361" r:id="rId717"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F361" r:id="rId718"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E362" r:id="rId719"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F362" r:id="rId720"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E363" r:id="rId721"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F363" r:id="rId722"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E364" r:id="rId723"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F364" r:id="rId724"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E365" r:id="rId725"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F365" r:id="rId726"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E366" r:id="rId727"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F366" r:id="rId728"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E367" r:id="rId729"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F367" r:id="rId730"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E368" r:id="rId731"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F368" r:id="rId732"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E369" r:id="rId733"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F369" r:id="rId734"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E370" r:id="rId735"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F370" r:id="rId736"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E371" r:id="rId737"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F371" r:id="rId738"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E372" r:id="rId739"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F372" r:id="rId740"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E373" r:id="rId741"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F373" r:id="rId742"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E374" r:id="rId743"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F374" r:id="rId744"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E375" r:id="rId745"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F375" r:id="rId746"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E376" r:id="rId747"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F376" r:id="rId748"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E377" r:id="rId749"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F377" r:id="rId750"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E378" r:id="rId751"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F378" r:id="rId752"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E379" r:id="rId753"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F379" r:id="rId754"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E380" r:id="rId755"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F380" r:id="rId756"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E381" r:id="rId757"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F381" r:id="rId758"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E382" r:id="rId759"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F382" r:id="rId760"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E383" r:id="rId761"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F383" r:id="rId762"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E384" r:id="rId763"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F384" r:id="rId764"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E385" r:id="rId765"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F385" r:id="rId766"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E386" r:id="rId767"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F386" r:id="rId768"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E387" r:id="rId769"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F387" r:id="rId770"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E388" r:id="rId771"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F388" r:id="rId772"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E389" r:id="rId773"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F389" r:id="rId774"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E390" r:id="rId775"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F390" r:id="rId776"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E391" r:id="rId777"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F391" r:id="rId778"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E392" r:id="rId779"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F392" r:id="rId780"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E393" r:id="rId781"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F393" r:id="rId782"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E394" r:id="rId783"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F394" r:id="rId784"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E395" r:id="rId785"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F395" r:id="rId786"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E396" r:id="rId787"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F396" r:id="rId788"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E397" r:id="rId789"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F397" r:id="rId790"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E398" r:id="rId791"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F398" r:id="rId792"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E399" r:id="rId793"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F399" r:id="rId794"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E400" r:id="rId795"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F400" r:id="rId796"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E401" r:id="rId797"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F401" r:id="rId798"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E402" r:id="rId799"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F402" r:id="rId800"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F403" r:id="rId801"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E404" r:id="rId802"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F404" r:id="rId803"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E405" r:id="rId804"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F405" r:id="rId805"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E406" r:id="rId806"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F406" r:id="rId807"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E407" r:id="rId808"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F407" r:id="rId809"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E408" r:id="rId810"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F408" r:id="rId811"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E409" r:id="rId812"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F409" r:id="rId813"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E410" r:id="rId814"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F410" r:id="rId815"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F411" r:id="rId816"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F78" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F79" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F80" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F81" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F82" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F83" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F84" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F85" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F86" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F87" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F88" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F89" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F90" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F91" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F92" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F93" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F94" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F95" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F96" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F97" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F98" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F99" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F100" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F101" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F102" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F103" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F104" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F105" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F106" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F107" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F108" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F109" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F110" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F111" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F112" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F113" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F114" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F115" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F116" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F117" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F118" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F119" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F120" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F121" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F122" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F123" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F124" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F125" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F126" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F127" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F128" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F129" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F130" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F131" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F132" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F133" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F134" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F135" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F136" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F137" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F138" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F139" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F140" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F141" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F142" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F143" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F144" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F145" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F146" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F147" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F148" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F149" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F150" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F151" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F152" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F153" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F154" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F155" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F156" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F157" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F158" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F159" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F160" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F161" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F162" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F163" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F164" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F165" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F166" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F167" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F168" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F169" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F170" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F171" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F172" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E173" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F173" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F174" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E175" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F175" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E176" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F176" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F177" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E178" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F178" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F179" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E180" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F180" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E181" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F181" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F182" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F183" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F184" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F185" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F186" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F187" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F188" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F189" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F190" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F191" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F192" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F193" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E194" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F194" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F195" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F196" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F197" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F198" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F199" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F200" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E201" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F201" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F202" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F203" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F204" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F205" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F206" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F207" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E208" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F208" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F209" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E210" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F210" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E211" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F211" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E212" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F212" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E213" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F213" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E214" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F214" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E215" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F215" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E216" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F216" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E217" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F217" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E218" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F218" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E219" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F219" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E220" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F220" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E221" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F221" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E222" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F222" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E223" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F223" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F224" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E225" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F225" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E226" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F226" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E227" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F227" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E228" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F228" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E229" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F229" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E230" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F230" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E231" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F231" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E232" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F232" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E233" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F233" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E234" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F234" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E235" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F235" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E236" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F236" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E237" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F237" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E238" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F238" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E239" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F239" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E240" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F240" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E241" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F241" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E242" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F242" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E243" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F243" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E244" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F244" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E245" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F245" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E246" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F246" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E247" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F247" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E248" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F248" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E249" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F249" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E250" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F250" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E251" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F251" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E252" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F252" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E253" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F253" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E254" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F254" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E255" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F255" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E256" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F256" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E257" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F257" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E258" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F258" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E259" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F259" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E260" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F260" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E261" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F261" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E262" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F262" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E263" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F263" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E264" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F264" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E265" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F265" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E266" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F266" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E267" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F267" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E268" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F268" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E269" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F269" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E270" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F270" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E271" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F271" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E272" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F272" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E273" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F273" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E274" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F274" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E275" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F275" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E276" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F276" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E277" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F277" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E278" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F278" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E279" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F279" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E280" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F280" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E281" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F281" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E282" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F282" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E283" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F283" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E284" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F284" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E285" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F285" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E286" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F286" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E287" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F287" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E288" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F288" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E289" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F289" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E290" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F290" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E291" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F291" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E292" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F292" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E293" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F293" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E294" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F294" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E295" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F295" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E296" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F296" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E297" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F297" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E298" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F298" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E299" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F299" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E300" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F300" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E301" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F301" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E302" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F302" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E303" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F303" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E304" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F304" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E305" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F305" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E306" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F306" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E307" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F307" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E308" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F308" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E309" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F309" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E310" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F310" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E311" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F311" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E312" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F312" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E313" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F313" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E314" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F314" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E315" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F315" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E316" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F316" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E317" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F317" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E318" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F318" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E319" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F319" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E320" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F320" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E321" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F321" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E322" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F322" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E323" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F323" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E324" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F324" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E325" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F325" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E326" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F326" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E327" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F327" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E328" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F328" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E329" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F329" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E330" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F330" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E331" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F331" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E332" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F332" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E333" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F333" r:id="rId661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E334" r:id="rId662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F334" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E335" r:id="rId664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F335" r:id="rId665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E336" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F336" r:id="rId667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E337" r:id="rId668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F337" r:id="rId669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E338" r:id="rId670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F338" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E339" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F339" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E340" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F340" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E341" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F341" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E342" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F342" r:id="rId679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E343" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F343" r:id="rId681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E344" r:id="rId682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F344" r:id="rId683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E345" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F345" r:id="rId685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E346" r:id="rId686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F346" r:id="rId687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E347" r:id="rId688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F347" r:id="rId689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E348" r:id="rId690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F348" r:id="rId691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E349" r:id="rId692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F349" r:id="rId693"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E350" r:id="rId694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F350" r:id="rId695"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E351" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F351" r:id="rId697"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E352" r:id="rId698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F352" r:id="rId699"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E353" r:id="rId700"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F353" r:id="rId701"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E354" r:id="rId702"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F354" r:id="rId703"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E355" r:id="rId704"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F355" r:id="rId705"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E356" r:id="rId706"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F356" r:id="rId707"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E357" r:id="rId708"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F357" r:id="rId709"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E358" r:id="rId710"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F358" r:id="rId711"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E359" r:id="rId712"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F359" r:id="rId713"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E360" r:id="rId714"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F360" r:id="rId715"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E361" r:id="rId716"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F361" r:id="rId717"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E362" r:id="rId718"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F362" r:id="rId719"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E363" r:id="rId720"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F363" r:id="rId721"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E364" r:id="rId722"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F364" r:id="rId723"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E365" r:id="rId724"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F365" r:id="rId725"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E366" r:id="rId726"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F366" r:id="rId727"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E367" r:id="rId728"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F367" r:id="rId729"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E368" r:id="rId730"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F368" r:id="rId731"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E369" r:id="rId732"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F369" r:id="rId733"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E370" r:id="rId734"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F370" r:id="rId735"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E371" r:id="rId736"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F371" r:id="rId737"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E372" r:id="rId738"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F372" r:id="rId739"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E373" r:id="rId740"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F373" r:id="rId741"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E374" r:id="rId742"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F374" r:id="rId743"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E375" r:id="rId744"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F375" r:id="rId745"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E376" r:id="rId746"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F376" r:id="rId747"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E377" r:id="rId748"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F377" r:id="rId749"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E378" r:id="rId750"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F378" r:id="rId751"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E379" r:id="rId752"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F379" r:id="rId753"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E380" r:id="rId754"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F380" r:id="rId755"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E381" r:id="rId756"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F381" r:id="rId757"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E382" r:id="rId758"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F382" r:id="rId759"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E383" r:id="rId760"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F383" r:id="rId761"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E384" r:id="rId762"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F384" r:id="rId763"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E385" r:id="rId764"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F385" r:id="rId765"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E386" r:id="rId766"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F386" r:id="rId767"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E387" r:id="rId768"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F387" r:id="rId769"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E388" r:id="rId770"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F388" r:id="rId771"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E389" r:id="rId772"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F389" r:id="rId773"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E390" r:id="rId774"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F390" r:id="rId775"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E391" r:id="rId776"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F391" r:id="rId777"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E392" r:id="rId778"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F392" r:id="rId779"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E393" r:id="rId780"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F393" r:id="rId781"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E394" r:id="rId782"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F394" r:id="rId783"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E395" r:id="rId784"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F395" r:id="rId785"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E396" r:id="rId786"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F396" r:id="rId787"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E397" r:id="rId788"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F397" r:id="rId789"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E398" r:id="rId790"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F398" r:id="rId791"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E399" r:id="rId792"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F399" r:id="rId793"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E400" r:id="rId794"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F400" r:id="rId795"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E401" r:id="rId796"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F401" r:id="rId797"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E402" r:id="rId798"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F402" r:id="rId799"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F403" r:id="rId800"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E404" r:id="rId801"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F404" r:id="rId802"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E405" r:id="rId803"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F405" r:id="rId804"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E406" r:id="rId805"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F406" r:id="rId806"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E407" r:id="rId807"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F407" r:id="rId808"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E408" r:id="rId809"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F408" r:id="rId810"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E409" r:id="rId811"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F409" r:id="rId812"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E410" r:id="rId813"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F410" r:id="rId814"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F411" r:id="rId815"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-04 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-05 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">The process runs four stages for the Summer Internship: 1. Online application at careers.blackrock.com: one program, up to two functions, resume. Choose your two functions deliberately, because withdrawing bars you from reapplying to the program that year. 2. Pre-interview assessment. An email link </t>
+          <t>The process runs four stages for the Summer Internship: Finance · 5-minute preview Here is one thing people in this job actually do. Sound like you? 📊 Check how last month's spending compared to the plan That's me Not for me Either answer starts the 5-minute lab. No account needed. 1. Online applica</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr"/>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Watchlist'!$A$2:$K$411</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Underclassman programs'!$A$2:$F$149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Underclassman programs'!$A$2:$F$147</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-05 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-06 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>The process runs four stages for the Summer Internship: Finance · 5-minute preview Here is one thing people in this job actually do. Sound like you? 📊 Check how last month's spending compared to the plan That's me Not for me Either answer starts the 5-minute lab. No account needed. 1. Online applica</t>
+          <t xml:space="preserve">The process runs four stages for the Summer Internship: Finance · 5-minute preview See what this job actually feels like Try a quick task based on the kind of work you'd do in a real role. A company's revenue keeps growing, but its profit doesn't. Can you figure out why from the numbers? Try it Not </t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr"/>
@@ -16560,7 +16560,7 @@
       </c>
       <c r="D288" s="6" t="inlineStr">
         <is>
-          <t>7 umbrella tracks across 16 US pipeline postings, plus co-ops and team-specific roles</t>
+          <t>Software Engineering; Machine Learning &amp; AI; Hardware Engineering; Hardware Technologies (Silicon); Engineering Program Management  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E288" s="7" t="inlineStr">
@@ -16841,7 +16841,7 @@
       </c>
       <c r="D293" s="6" t="inlineStr">
         <is>
-          <t>20+ distinct intern tracks across engineering, data, product, design, partnerships, and marketing</t>
+          <t>Software Engineer Intern; Community Apprenticeship (SWE); Data Scientist PhD Intern; Applied Scientist PhD Intern  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E293" s="7" t="inlineStr">
@@ -17008,7 +17008,7 @@
       </c>
       <c r="D296" s="6" t="inlineStr">
         <is>
-          <t>15 across IB, Markets, Research, Technology, Operations, and more</t>
+          <t>Technology; Markets Quantitative Analytics  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E296" s="7" t="inlineStr">
@@ -17021,7 +17021,11 @@
           <t>guide</t>
         </is>
       </c>
-      <c r="G296" s="6" t="inlineStr"/>
+      <c r="G296" s="6" t="inlineStr">
+        <is>
+          <t>Barclays runs a four-stage funnel, and the rolling timeline means each stage can start within days of the previous one: 1. Apply through search.jobs.barclays or the Workday portal with your resume, transcript, and short application questions. Barclays posts separate listings per track, so choose you</t>
+        </is>
+      </c>
       <c r="H296" s="6" t="inlineStr">
         <is>
           <t>No. Barclays explicitly states it will not sponsor applicants for work visas or provide any employment-based immigration sponsorship for internships, post-graduation programs, or permanent employment. This includes no as</t>
@@ -21488,7 +21492,7 @@
       </c>
       <c r="D376" s="6" t="inlineStr">
         <is>
-          <t>Quantitative Trader – Intern; Quantitative Research Analyst – Intern (BS/MS); Quantitative Researcher – PhD Intern; Software Engineer – Intern  (4 of 6 tracks)</t>
+          <t>Quantitative Trader – Intern; Quantitative Research Analyst – Intern (BS/MS); Quantitative Researcher – PhD Intern; Software Engineer – Intern  (4 of 12 tracks)</t>
         </is>
       </c>
       <c r="E376" s="7" t="inlineStr">
@@ -34961,7 +34965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F149"/>
+  <dimension ref="A1:F147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -37998,17 +38002,17 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>🔥 CLOSING SOON]</t>
+          <t>✅ OPEN]</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>OpenAI Student Collective (Campus Lead) — Deadline: Aug 31, 2026 (Japan, Korea, UK, Germany, France; US/Canada/India Cohort Closed)</t>
+          <t>Pearson Campus Ambassador — Deadline: Rolling</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr"/>
@@ -38031,12 +38035,12 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Princess Polly</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>Pearson Campus Ambassador — Deadline: Rolling</t>
+          <t>College Ambassador — Deadline: Rolling</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr"/>
@@ -38059,12 +38063,12 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>Princess Polly</t>
+          <t>Red Bull</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>College Ambassador — Deadline: Rolling</t>
+          <t>Student Marketeer — Deadline: Rolling</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr"/>
@@ -38082,17 +38086,17 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>Summer of Code</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>Red Bull</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>Student Marketeer — Deadline: Rolling</t>
+          <t>open-source, stipend, open to intl</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr"/>
@@ -38103,19 +38107,19 @@
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>Ambassador Programs</t>
+          <t>Pipelines (programs always open)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>Summer of Code</t>
+          <t>Outreachy</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Outreachy</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
@@ -38138,20 +38142,24 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>Outreachy</t>
+          <t>Software Undergrad Engineering Internship</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>Outreachy</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>open-source, stipend, open to intl</t>
-        </is>
-      </c>
-      <c r="D110" s="5" t="inlineStr"/>
+          <t>SWE intern (undergrad)</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>rolling</t>
+        </is>
+      </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
           <t>apply</t>
@@ -38159,14 +38167,14 @@
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>Pipelines (programs always open)</t>
+          <t>Pipelines (programs open now)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>Software Undergrad Engineering Internship</t>
+          <t>Machine Learning &amp; AI Undergrad Internship</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
@@ -38176,7 +38184,7 @@
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>SWE intern (undergrad)</t>
+          <t>ML / AI intern (undergrad)</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
@@ -38198,7 +38206,7 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; AI Undergrad Internship</t>
+          <t>Hardware Undergrad Engineering Internship</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
@@ -38208,7 +38216,7 @@
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>ML / AI intern (undergrad)</t>
+          <t>hardware intern (undergrad)</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
@@ -38230,22 +38238,22 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>Hardware Undergrad Engineering Internship</t>
+          <t>Student Fellows Program</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>hardware intern (undergrad)</t>
+          <t>data and AI fellowship</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>rolling</t>
+          <t>check site</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr">
@@ -38262,22 +38270,22 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>Student Fellows Program</t>
+          <t>2027 US Summer Internship, Early Interest</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Dexcom</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>data and AI fellowship</t>
+          <t>early interest pipeline</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>check site</t>
+          <t>rolling</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr">
@@ -38294,17 +38302,17 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>2027 US Summer Internship, Early Interest</t>
+          <t>Learn Student Ambassadors</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>Dexcom</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>early interest pipeline</t>
+          <t>ambassador program</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
@@ -38326,17 +38334,17 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>Learn Student Ambassadors</t>
+          <t>MLH Fellowship</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>MLH</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>ambassador program</t>
+          <t>remote SWE fellowship, stipend</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
@@ -38358,22 +38366,22 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>MLH Fellowship</t>
+          <t>Neo Scholars</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>MLH</t>
+          <t>Neo</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>remote SWE fellowship, stipend</t>
+          <t>CS undergrad fellowship</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>rolling</t>
+          <t>approx June 14 to 30, 2026</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr">
@@ -38390,22 +38398,22 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>Neo Scholars</t>
+          <t>AI Builder, Emerging Talent</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>Neo</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>CS undergrad fellowship</t>
+          <t>emerging talent program</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>approx June 14 to 30, 2026</t>
+          <t>check site</t>
         </is>
       </c>
       <c r="E118" s="7" t="inlineStr">
@@ -38422,22 +38430,22 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>AI Builder, Emerging Talent</t>
+          <t>2027 Summer Internships, Express Your Interest</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Schonfeld</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>emerging talent program</t>
+          <t>express interest pipeline, full roles open Aug 2026</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>check site</t>
+          <t>rolling</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr">
@@ -38454,24 +38462,20 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>2027 Summer Internships, Express Your Interest</t>
+          <t>⏳ OPENS SOON]</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>Schonfeld</t>
+          <t>Ayn Rand Institute</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>express interest pipeline, full roles open Aug 2026</t>
-        </is>
-      </c>
-      <c r="D120" s="5" t="inlineStr">
-        <is>
-          <t>rolling</t>
-        </is>
-      </c>
+          <t>Fountainhead Essay Contest (Grades 11–12) — Deadline: Sep 13, 2026 (Anthem contest closed May 31, 2026)</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr"/>
       <c r="E120" s="7" t="inlineStr">
         <is>
           <t>apply</t>
@@ -38479,24 +38483,24 @@
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>Pipelines (programs open now)</t>
+          <t>Rising Freshmen &amp; Class of 2030 Opportunities</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>⏳ OPENS SOON]</t>
+          <t>✅ OPEN]</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>Ayn Rand Institute</t>
+          <t>Coca-Cola Scholars Foundation</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>Fountainhead Essay Contest (Grades 11–12) — Deadline: Sep 13, 2026 (Anthem contest closed May 31, 2026)</t>
+          <t>Coca-Cola Scholars Program (HS Senior; 3.0+ GPA)</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr"/>
@@ -38514,17 +38518,17 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>🔥 CLOSING SOON]</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>Coca-Cola Scholars Foundation</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>Coca-Cola Scholars Program (HS Senior; 3.0+ GPA)</t>
+          <t>The Gates Scholarship (Low-Income Minority HS Seniors)</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr"/>
@@ -38542,17 +38546,17 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>🔥 CLOSING SOON]</t>
+          <t>✅ OPEN]</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Hagan Scholarship Foundation</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>The Gates Scholarship (Low-Income Minority HS Seniors)</t>
+          <t>Hagan Scholarship (HS Senior; 3.5+ GPA; Household Income ≤ $125K; 4-Yr Non-Profit College — No CC/Online)</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr"/>
@@ -38570,17 +38574,17 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>⏳ OPENS SOON]</t>
+          <t>✅ OPEN]</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>Hagan Scholarship Foundation</t>
+          <t>Jane Street</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>Hagan Scholarship (HS Senior; 3.5+ GPA; Household Income ≤ $125K; 4-Yr Non-Profit College — No CC/Online)</t>
+          <t>WiSE - Women in Science &amp; Engineering (Class of 2030)</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr"/>
@@ -38603,12 +38607,12 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>Jane Street</t>
+          <t>National Merit Scholarship Corporation</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>WiSE - Women in Science &amp; Engineering (Class of 2030)</t>
+          <t>National Merit Scholarship (PSAT/NMSQT Junior Year)</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr"/>
@@ -38631,12 +38635,12 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>National Merit Scholarship Corporation</t>
+          <t>Optimist International</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>National Merit Scholarship (PSAT/NMSQT Junior Year)</t>
+          <t>Optimist International Essay Contest (Under 19 on Oct 1; 700–800 word essay; 2026-27 topic announced)</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr"/>
@@ -38659,12 +38663,12 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>Optimist International</t>
+          <t>Posse Foundation</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>Optimist International Essay Contest (Under 19 on Oct 1; 700–800 word essay; 2026-27 topic announced)</t>
+          <t>Posse Scholarship (Nomination-Based; Partner Cities)</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr"/>
@@ -38687,12 +38691,12 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>Posse Foundation</t>
+          <t>QuestBridge</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>Posse Scholarship (Nomination-Based; Partner Cities)</t>
+          <t>National College Match (HS Senior; Low-Income)</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr"/>
@@ -38715,12 +38719,12 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>QuestBridge</t>
+          <t>Regeneron / Society for Science</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>National College Match (HS Senior; Low-Income)</t>
+          <t>Regeneron Science Talent Search (HS Senior STEM Research)</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr"/>
@@ -38743,12 +38747,12 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>Regeneron / Society for Science</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>Regeneron Science Talent Search (HS Senior STEM Research)</t>
+          <t>Adobe NEXT// Campus Leader — Deadline: Check site</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr"/>
@@ -38759,7 +38763,7 @@
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>Rising Freshmen &amp; Class of 2030 Opportunities</t>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
         </is>
       </c>
     </row>
@@ -38771,12 +38775,12 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Career Pathways Initiative</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>Adobe NEXT// Campus Leader — Deadline: Check site</t>
+          <t>Career Pathways Initiative Fellowship — Deadline: Rolling</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr"/>
@@ -38799,12 +38803,12 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>Career Pathways Initiative</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>Career Pathways Initiative Fellowship — Deadline: Rolling</t>
+          <t>Databricks Student Fellows Program — Deadline: Check site</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr"/>
@@ -38827,12 +38831,12 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>ElevenLabs</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>Databricks Student Fellows Program — Deadline: Check site</t>
+          <t>ElevenLabs Ambassador Program — Deadline: Rolling</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr"/>
@@ -38855,12 +38859,12 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>ElevenLabs</t>
+          <t>GirlsWhoML</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>ElevenLabs Ambassador Program — Deadline: Rolling</t>
+          <t>Thinking About Thinking 2026 Ambassador Programme — Deadline: Check site</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr"/>
@@ -38883,12 +38887,12 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>GirlsWhoML</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>Thinking About Thinking 2026 Ambassador Programme — Deadline: Check site</t>
+          <t>AI Fellowship Program — Deadline: Check site</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr"/>
@@ -38911,12 +38915,12 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>IOScholarships</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>AI Fellowship Program — Deadline: Check site</t>
+          <t>AWS re/Start — Deadline: Rolling (Cohort: Sep 15–Dec 15, 2026)</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr"/>
@@ -38939,12 +38943,12 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>IOScholarships</t>
+          <t>Jane Street</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>AWS re/Start — Deadline: Rolling (Cohort: Sep 15–Dec 15, 2026)</t>
+          <t>FTTP — First-Year Trading &amp; Technology Program — Deadline: Rolling (Sign Up to Be Notified)</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr"/>
@@ -38967,12 +38971,12 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>Jane Street</t>
+          <t>Lime Connect</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>FTTP — First-Year Trading &amp; Technology Program — Deadline: Rolling (Sign Up to Be Notified)</t>
+          <t>Lime Connect Network Membership — Deadline: Rolling</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr"/>
@@ -38995,12 +38999,12 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>Lime Connect</t>
+          <t>MLT (Management Leadership for Tomorrow)</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>Lime Connect Network Membership — Deadline: Rolling</t>
+          <t>MLT Career Prep (Class of 2029) — Deadline: Aug 1, 2026 – Jan 15, 2027 (Phased)</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr"/>
@@ -39023,12 +39027,12 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>MLH (Major League Hacking)</t>
+          <t>NSN (National Sales Network)</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>MLH Fellowship — Deadline: Aug 31, 2026 (Fall Batch: Starts Sep 14, 2026)</t>
+          <t>2026 NSN Student Sales &amp; Marketing Conference — Deadline: Rolling (Event: Sep 12–14, 2026)</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr"/>
@@ -39051,12 +39055,12 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>MLT (Management Leadership for Tomorrow)</t>
+          <t>OpenTrade</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>MLT Career Prep (Class of 2029) — Deadline: Aug 1, 2026 – Jan 15, 2027 (Phased)</t>
+          <t>OpenTrade Fellowship — Deadline: Rolling (Limited Spots)</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr"/>
@@ -39074,17 +39078,17 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>🔥 CLOSING SOON]</t>
+          <t>✅ OPEN]</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>NSN (National Sales Network)</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>2026 NSN Student Sales &amp; Marketing Conference — Deadline: Rolling (Event: Sep 12–14, 2026)</t>
+          <t>PwC AI Externships — Deadline: Rolling</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr"/>
@@ -39107,12 +39111,12 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>OpenTrade</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>OpenTrade Fellowship — Deadline: Rolling (Limited Spots)</t>
+          <t>Campus Leaders — Deadline: Rolling</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr"/>
@@ -39135,12 +39139,12 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>SHPE</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>PwC AI Externships — Deadline: Rolling</t>
+          <t>2026 SHPE National Convention — Deadline: Check site (Event: Oct 28–31, 2026)</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr"/>
@@ -39163,12 +39167,12 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>Campus Leaders — Deadline: Rolling</t>
+          <t>The Home Depot Externships (Multiple Tracks) — Deadline: Varies by Externship (Check Hub for Open Tracks)</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr"/>
@@ -39191,12 +39195,12 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>SHPE</t>
+          <t>WomenHack</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>2026 SHPE National Convention — Deadline: Check site (Event: Oct 28–31, 2026)</t>
+          <t>Women in Tech Career Fair — Deadline: Varies per event</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr"/>
@@ -39219,12 +39223,12 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>The Home Depot Externships (Multiple Tracks) — Deadline: Varies by Externship (Check Hub for Open Tracks)</t>
+          <t>Student Researcher, BS/MS, Fall 2026 — Deadline: Nov 27, 2026 (Rolling; May Close Earlier)</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr"/>
@@ -39235,68 +39239,12 @@
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="3" t="inlineStr">
-        <is>
-          <t>✅ OPEN]</t>
-        </is>
-      </c>
-      <c r="B148" s="5" t="inlineStr">
-        <is>
-          <t>WomenHack</t>
-        </is>
-      </c>
-      <c r="C148" s="6" t="inlineStr">
-        <is>
-          <t>Women in Tech Career Fair — Deadline: Varies per event</t>
-        </is>
-      </c>
-      <c r="D148" s="5" t="inlineStr"/>
-      <c r="E148" s="7" t="inlineStr">
-        <is>
-          <t>apply</t>
-        </is>
-      </c>
-      <c r="F148" s="5" t="inlineStr">
-        <is>
-          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="3" t="inlineStr">
-        <is>
-          <t>✅ OPEN]</t>
-        </is>
-      </c>
-      <c r="B149" s="5" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="C149" s="6" t="inlineStr">
-        <is>
-          <t>Student Researcher, BS/MS, Fall 2026 — Deadline: Nov 27, 2026 (Rolling; May Close Earlier)</t>
-        </is>
-      </c>
-      <c r="D149" s="5" t="inlineStr"/>
-      <c r="E149" s="7" t="inlineStr">
-        <is>
-          <t>apply</t>
-        </is>
-      </c>
-      <c r="F149" s="5" t="inlineStr">
-        <is>
           <t>Underclassmen Research Programs</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:F149"/>
+  <autoFilter ref="A2:F147"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -39446,8 +39394,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId143"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId147"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-06 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-07 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-07 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-08 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-08 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-09 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>8+ intern and apprentice tracks (STEP, SWE, Student Researcher, Research, Silicon, UX and more)</t>
+          <t>STEP; Software Engineering Intern; Student Researcher; Research Scientist Intern (PhD); Silicon / Hardware Engineering Intern  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
@@ -16613,7 +16613,7 @@
       </c>
       <c r="D289" s="6" t="inlineStr">
         <is>
-          <t>10+ across Engineering, Operations, Asset Servicing, Finance, Investment Management, and more</t>
+          <t>Engineering / Developer  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E289" s="7" t="inlineStr">
@@ -16727,7 +16727,7 @@
       </c>
       <c r="D291" s="6" t="inlineStr">
         <is>
-          <t>10+ tracks: SDE, Applied Scientist, Data Scientist, Finance Rotational, BIE, Data Engineer, and more</t>
+          <t>SDE Intern; Applied Scientist Intern; Data Scientist Intern; Business Intelligence Engineer Intern; Data Engineer Intern  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E291" s="7" t="inlineStr">

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Watchlist'!$A$2:$K$411</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Underclassman programs'!$A$2:$F$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Underclassman programs'!$A$2:$F$149</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-09 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-10 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -34965,7 +34965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F147"/>
+  <dimension ref="A1:F149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -38971,12 +38971,12 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>Lime Connect</t>
+          <t>Jane Street</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>Lime Connect Network Membership — Deadline: Rolling</t>
+          <t>Bridge — Deadline: Rolling (Sign Up to Be Notified)</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr"/>
@@ -38999,12 +38999,12 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>MLT (Management Leadership for Tomorrow)</t>
+          <t>Jane Street</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>MLT Career Prep (Class of 2029) — Deadline: Aug 1, 2026 – Jan 15, 2027 (Phased)</t>
+          <t>FOCUS — Deadline: Rolling (Sign Up to Be Notified)</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr"/>
@@ -39022,17 +39022,17 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>🔥 CLOSING SOON]</t>
+          <t>✅ OPEN]</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>NSN (National Sales Network)</t>
+          <t>Lime Connect</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>2026 NSN Student Sales &amp; Marketing Conference — Deadline: Rolling (Event: Sep 12–14, 2026)</t>
+          <t>Lime Connect Network Membership — Deadline: Rolling</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr"/>
@@ -39055,12 +39055,12 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>OpenTrade</t>
+          <t>MLT (Management Leadership for Tomorrow)</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>OpenTrade Fellowship — Deadline: Rolling (Limited Spots)</t>
+          <t>MLT Career Prep (Class of 2029) — Deadline: Aug 1, 2026 – Jan 15, 2027 (Phased)</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr"/>
@@ -39078,17 +39078,17 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>🔥 CLOSING SOON]</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>NSN (National Sales Network)</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>PwC AI Externships — Deadline: Rolling</t>
+          <t>2026 NSN Student Sales &amp; Marketing Conference — Deadline: Rolling (Event: Sep 12–14, 2026)</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr"/>
@@ -39111,12 +39111,12 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>OpenTrade</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>Campus Leaders — Deadline: Rolling</t>
+          <t>OpenTrade Fellowship — Deadline: Rolling (Limited Spots)</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr"/>
@@ -39139,12 +39139,12 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>SHPE</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>2026 SHPE National Convention — Deadline: Check site (Event: Oct 28–31, 2026)</t>
+          <t>PwC AI Externships — Deadline: Rolling</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr"/>
@@ -39167,12 +39167,12 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>The Home Depot Externships (Multiple Tracks) — Deadline: Varies by Externship (Check Hub for Open Tracks)</t>
+          <t>Campus Leaders — Deadline: Rolling</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr"/>
@@ -39195,12 +39195,12 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>WomenHack</t>
+          <t>SHPE</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>Women in Tech Career Fair — Deadline: Varies per event</t>
+          <t>2026 SHPE National Convention — Deadline: Check site (Event: Oct 28–31, 2026)</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr"/>
@@ -39223,12 +39223,12 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>Student Researcher, BS/MS, Fall 2026 — Deadline: Nov 27, 2026 (Rolling; May Close Earlier)</t>
+          <t>The Home Depot Externships (Multiple Tracks) — Deadline: Varies by Externship (Check Hub for Open Tracks)</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr"/>
@@ -39239,12 +39239,68 @@
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>WomenHack</t>
+        </is>
+      </c>
+      <c r="C148" s="6" t="inlineStr">
+        <is>
+          <t>Women in Tech Career Fair — Deadline: Varies per event</t>
+        </is>
+      </c>
+      <c r="D148" s="5" t="inlineStr"/>
+      <c r="E148" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F148" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="inlineStr">
+        <is>
+          <t>Student Researcher, BS/MS, Fall 2026 — Deadline: Nov 27, 2026 (Rolling; May Close Earlier)</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr"/>
+      <c r="E149" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F149" s="5" t="inlineStr">
+        <is>
           <t>Underclassmen Research Programs</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:F147"/>
+  <autoFilter ref="A2:F149"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -39394,6 +39450,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId143"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId147"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-10 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-11 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-11 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-12 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
